--- a/ts_1_to_2.xlsx
+++ b/ts_1_to_2.xlsx
@@ -540,7 +540,7 @@
         <v>482538.4155253794</v>
       </c>
       <c r="L2" t="n">
-        <v>-388.3192861833203</v>
+        <v>-1019532285.874308</v>
       </c>
       <c r="M2" t="n">
         <v>-1019038750.388882</v>
@@ -587,7 +587,7 @@
         <v>470108.0886346833</v>
       </c>
       <c r="L3" t="n">
-        <v>-388.3192861833203</v>
+        <v>-1019532285.874308</v>
       </c>
       <c r="M3" t="n">
         <v>-1019036683.212686</v>
@@ -634,7 +634,7 @@
         <v>456233.3992678866</v>
       </c>
       <c r="L4" t="n">
-        <v>-388.3192861833203</v>
+        <v>-1019532285.874308</v>
       </c>
       <c r="M4" t="n">
         <v>-1019033845.812366</v>
@@ -681,7 +681,7 @@
         <v>441274.2722636915</v>
       </c>
       <c r="L5" t="n">
-        <v>-388.3192861833203</v>
+        <v>-1019532285.874308</v>
       </c>
       <c r="M5" t="n">
         <v>-1019030098.528417</v>
@@ -728,7 +728,7 @@
         <v>425263.5480489656</v>
       </c>
       <c r="L6" t="n">
-        <v>-388.3192861833203</v>
+        <v>-1019532285.874308</v>
       </c>
       <c r="M6" t="n">
         <v>-1019025178.622498</v>
@@ -775,7 +775,7 @@
         <v>408121.8037728688</v>
       </c>
       <c r="L7" t="n">
-        <v>-388.3192861833203</v>
+        <v>-1019532285.874308</v>
       </c>
       <c r="M7" t="n">
         <v>-1019018882.850361</v>
@@ -822,7 +822,7 @@
         <v>389767.1184718886</v>
       </c>
       <c r="L8" t="n">
-        <v>-388.3192861833203</v>
+        <v>-1019532285.874308</v>
       </c>
       <c r="M8" t="n">
         <v>-1019011137.970862</v>
@@ -869,7 +869,7 @@
         <v>370132.3683450489</v>
       </c>
       <c r="L9" t="n">
-        <v>-388.3192861833203</v>
+        <v>-1019532285.874308</v>
       </c>
       <c r="M9" t="n">
         <v>-1019001978.937088</v>
@@ -916,7 +916,7 @@
         <v>349170.9089189661</v>
       </c>
       <c r="L10" t="n">
-        <v>-388.3192861833203</v>
+        <v>-1019532285.874308</v>
       </c>
       <c r="M10" t="n">
         <v>-1018991503.330492</v>
@@ -963,7 +963,7 @@
         <v>326861.840933906</v>
       </c>
       <c r="L11" t="n">
-        <v>-388.3192861833203</v>
+        <v>-1019532285.874308</v>
       </c>
       <c r="M11" t="n">
         <v>-1018979833.775248</v>
@@ -1010,7 +1010,7 @@
         <v>303213.8556237391</v>
       </c>
       <c r="L12" t="n">
-        <v>-388.3192861833203</v>
+        <v>-1019532285.874308</v>
       </c>
       <c r="M12" t="n">
         <v>-1018967094.738608</v>
@@ -1057,7 +1057,7 @@
         <v>278266.5938814221</v>
       </c>
       <c r="L13" t="n">
-        <v>-388.3192861833203</v>
+        <v>-1019532285.874308</v>
       </c>
       <c r="M13" t="n">
         <v>-1018953400.999656</v>
@@ -1104,7 +1104,7 @@
         <v>252088.1626357383</v>
       </c>
       <c r="L14" t="n">
-        <v>-388.3192861833203</v>
+        <v>-1019532285.874308</v>
       </c>
       <c r="M14" t="n">
         <v>-1018938853.482581</v>
@@ -1151,7 +1151,7 @@
         <v>224769.1816273482</v>
       </c>
       <c r="L15" t="n">
-        <v>-388.3192861833203</v>
+        <v>-1019532285.874308</v>
       </c>
       <c r="M15" t="n">
         <v>-1018923539.015582</v>
@@ -1198,7 +1198,7 @@
         <v>196414.9509648217</v>
       </c>
       <c r="L16" t="n">
-        <v>-388.3192861833203</v>
+        <v>-1019532285.874308</v>
       </c>
       <c r="M16" t="n">
         <v>-1018907531.821719</v>
@@ -1245,7 +1245,7 @@
         <v>167137.4079539523</v>
       </c>
       <c r="L17" t="n">
-        <v>-388.3192861833203</v>
+        <v>-1019532285.874308</v>
       </c>
       <c r="M17" t="n">
         <v>-1018890895.530271</v>
@@ -1292,7 +1292,7 @@
         <v>137048.0704168289</v>
       </c>
       <c r="L18" t="n">
-        <v>-388.3192861833203</v>
+        <v>-1019532285.874308</v>
       </c>
       <c r="M18" t="n">
         <v>-1018873685.127248</v>
@@ -1339,7 +1339,7 @@
         <v>106252.5836100803</v>
       </c>
       <c r="L19" t="n">
-        <v>-388.3192861833203</v>
+        <v>-1019532285.874308</v>
       </c>
       <c r="M19" t="n">
         <v>-1018855948.619251</v>
@@ -1386,7 +1386,7 @@
         <v>74847.01535162458</v>
       </c>
       <c r="L20" t="n">
-        <v>-388.3192861833203</v>
+        <v>-1019532285.874308</v>
       </c>
       <c r="M20" t="n">
         <v>-1018837728.363861</v>
